--- a/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 6(CE EV)_70kW+160kW.xlsx
+++ b/config/auto_configs/2023_Hyundai_Hyundai_IONIQ 6(CE EV)_70kW+160kW.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3443,6 +3443,1216 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>IBU-TPMS</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>HMA_HK_01428</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>HMA_HK_01372</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ADAS_D</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>HMA_HK_01430</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>HMA_HK_01374</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ADAS_P</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>HMA_HK_01432</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>HMA_HK_01433</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>HMA_HK_01434</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>APSU</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HMA_HK_01435</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>AVN</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HMA_HK_01436</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HMA_HK_01437</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CCU_CCNF</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>HMA_HK_01438</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CCU_CGW</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>HMA_HK_01439</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>HMA_HK_01383</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>DAU</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>HMA_HK_01441</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>DCU</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>HMA_HK_01442</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>DHS_FL</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>HMA_HK_01443</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>DHS_FR</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>HMA_HK_01444</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>DSM-L</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>HMA_HK_01445</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>DSM-R</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>HMA_HK_01446</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>DVRS</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>HMA_HK_01447</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>HMA_HK_01448</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>E-Shifter</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>HMA_HK_01449</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>HMA_HK_01450</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>FVC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>HMA_HK_01451</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HUD</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>HMA_HK_01452</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HMA_HK_01453</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>IBU-BCM</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>HMA_HK_01454</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>IBU-IMM</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>HMA_HK_01455</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>IBU-SKU</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>HMA_HK_01456</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>ICC</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>HMA_HK_01457</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>ICCU</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>HMA_HK_01458</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ICU</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>HMA_HK_01459</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>IFS</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HMA_HK_01460</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MCU-F</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>HMA_HK_01461</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MCU-R</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>HMA_HK_01462</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MFS</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>HMA_HK_01463</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MLM</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>HMA_HK_01464</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>OCS</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HMA_HK_01465</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>OMS</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>HMA_HK_01466</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PCM</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>HMA_HK_01467</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>HMA_HK_01468</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PTM</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>HMA_HK_01469</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>RCR</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>HMA_HK_01470</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>HMA_HK_01471</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>RVMS</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HMA_HK_01472</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SBCM_AST</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>HMA_HK_01473</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SBCM_DRV</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>HMA_HK_01474</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SCU</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>HMA_HK_01475</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SHVU-F</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>HMA_HK_01476</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SHVU-R</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>HMA_HK_01477</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SWRC</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>HMA_HK_01478</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>VCMS</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>HMA_HK_01479</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VCU</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>HMA_HK_00596</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>HMA_HK_01481</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>WPC</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>HMA_HK_01482</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
